--- a/data/synthetic/messy_joinery/jobs spring - Marks copy.xlsx
+++ b/data/synthetic/messy_joinery/jobs spring - Marks copy.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>quote sent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
@@ -500,12 +500,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MATERIALS ORDERED</t>
+          <t>SITE SURVEY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -544,17 +544,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Snagging</t>
+          <t>site work started</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Sent </t>
+          <t>snagging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -625,49 +625,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Received </t>
+          <t>INVOICE SENT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J-1031</t>
+          <t>J-1030</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quote sent</t>
+          <t>Payment Received</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Accepted </t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>re-measure</t>
+          <t xml:space="preserve">Quote Accepted </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>client to confirm</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MATERIALS ORDERED</t>
+          <t>SITE SURVEY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>site work started</t>
+          <t>SITE SURVEY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>supplier late</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t>Materials Ordered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>invoice sent</t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -841,44 +841,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PAYMENT RECEIVED</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>done</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J-1032</t>
+          <t>J-1031</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quote Sent</t>
+          <t xml:space="preserve">Invoice Sent </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,27 +890,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J-1032</t>
+          <t>J-1031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Accepted </t>
+          <t xml:space="preserve">Payment Received </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>materials ordered</t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,22 +949,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site Work Started </t>
+          <t>Quote Accepted</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invoice Sent </t>
+          <t>Materials Ordered</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,66 +1030,66 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>payment received</t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J-1033</t>
+          <t>J-1032</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Sent </t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J-1033</t>
+          <t>J-1032</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>Invoice Sent</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1099,24 +1099,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J-1033</t>
+          <t>J-1032</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MATERIALS ORDERED</t>
+          <t>payment received</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Site Work Started </t>
+          <t>quote sent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>done</t>
         </is>
       </c>
     </row>
@@ -1165,22 +1165,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snagging </t>
+          <t>quote accepted</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Invoice Sent</t>
+          <t>Site Survey</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Payment Received </t>
+          <t>materials ordered</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>J-1034</t>
+          <t>J-1033</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quote Sent</t>
+          <t>Site Work Started</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>J-1034</t>
+          <t>J-1033</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t xml:space="preserve">Snagging </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,17 +1295,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J-1034</t>
+          <t>J-1033</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Materials Ordered</t>
+          <t>invoice sent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1315,34 +1315,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>J-1034</t>
+          <t>J-1033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Site Work Started</t>
+          <t>Payment Received</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Snagging Revisit</t>
+          <t>Quote Accepted</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>client to confirm</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>invoice sent</t>
+          <t xml:space="preserve">Site Survey </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t xml:space="preserve">Materials Ordered </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1457,17 +1457,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>J-1035</t>
+          <t>J-1034</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quote Sent </t>
+          <t>Site Work Started</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1477,19 +1477,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">Done </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>J-1035</t>
+          <t>J-1034</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quote Accepted</t>
+          <t>SNAGGING</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1511,44 +1511,44 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>J-1035</t>
+          <t>J-1034</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials Ordered </t>
+          <t>site work started</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Ciara McCrossan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>tbc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>J-1035</t>
+          <t>J-1034</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SITE WORK STARTED</t>
+          <t xml:space="preserve">Invoice Sent </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1558,34 +1558,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J-1035</t>
+          <t>J-1034</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>snagging</t>
+          <t xml:space="preserve">Payment Received </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1597,22 +1597,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Invoice Sent</t>
+          <t xml:space="preserve">Quote Sent </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
@@ -1624,44 +1624,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Payment Received</t>
+          <t xml:space="preserve">Quote Accepted </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>sorted</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1035</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>SITE SURVEY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1673,44 +1673,44 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1035</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t>Materials Ordered</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Paddy Lynch</t>
+          <t>Mark Deehan</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>J-1025</t>
+          <t>J-1035</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re-measure </t>
+          <t>SITE WORK STARTED</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1720,56 +1720,56 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done </t>
+          <t>sorted</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1035</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>QUOTE SENT</t>
+          <t>Snagging</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ciara McCrossan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>done</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>J-1026</t>
+          <t>J-1035</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>QUOTE ACCEPTED</t>
+          <t xml:space="preserve">Invoice Sent </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Mark Deehan</t>
+          <t>Paddy Lynch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1781,27 +1781,189 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>J-1035</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PAYMENT RECEIVED</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>J-1025</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote Sent </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>J-1025</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>quote accepted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>J-1025</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Site Survey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ciara McCrossan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>J-1026</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>materials ordered</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote Sent </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Paddy Lynch</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>sorted</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>J-1026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quote Accepted </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Paddy Lynch</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J-1026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>site survey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mark Deehan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>done</t>
         </is>
       </c>
     </row>

--- a/data/synthetic/messy_joinery/jobs spring - Marks copy.xlsx
+++ b/data/synthetic/messy_joinery/jobs spring - Marks copy.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
